--- a/artfynd/A 35702-2024 artfynd.xlsx
+++ b/artfynd/A 35702-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126367847</v>
       </c>
       <c r="B2" t="n">
-        <v>98272</v>
+        <v>98281</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>126367845</v>
       </c>
       <c r="B3" t="n">
-        <v>98272</v>
+        <v>98281</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35702-2024 artfynd.xlsx
+++ b/artfynd/A 35702-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Malin Schött , Anna Ljunggren</t>
+          <t>Anna Ljunggren, Malin Schött</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Malin Schött , Anna Ljunggren</t>
+          <t>Anna Ljunggren, Malin Schött</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 35702-2024 artfynd.xlsx
+++ b/artfynd/A 35702-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126367847</v>
+        <v>126367845</v>
       </c>
       <c r="B2" t="n">
-        <v>98281</v>
+        <v>99038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -701,19 +701,11 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -722,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346828</v>
+        <v>346814</v>
       </c>
       <c r="R2" t="n">
-        <v>6626436</v>
+        <v>6626492</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -757,22 +749,22 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>18:12</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>18:12</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Står på västra sidan av vägen i innerslänt.</t>
+          <t>9 exemplar på en sträcka av 10 meter. Står på västra sidan av vägen i ytterslänt och innerslänt.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Ljunggren, Malin Schött</t>
+          <t>Malin Schött, Anna Ljunggren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -803,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126367845</v>
+        <v>126367847</v>
       </c>
       <c r="B3" t="n">
-        <v>98281</v>
+        <v>99038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,11 +821,19 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346814</v>
+        <v>346828</v>
       </c>
       <c r="R3" t="n">
-        <v>6626492</v>
+        <v>6626436</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>9 exemplar på en sträcka av 10 meter. Står på västra sidan av vägen i ytterslänt och innerslänt.</t>
+          <t>Står på västra sidan av vägen i innerslänt.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +912,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Ljunggren, Malin Schött</t>
+          <t>Malin Schött, Anna Ljunggren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 35702-2024 artfynd.xlsx
+++ b/artfynd/A 35702-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -792,6 +797,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126367845</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -920,8 +930,17 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126367847</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>